--- a/artfynd/A 11176-2024 artfynd.xlsx
+++ b/artfynd/A 11176-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88915693</v>
+        <v>104764388</v>
       </c>
       <c r="B2" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kyrkjuves, Gtl</t>
+          <t>Gammelgarn Kyrkjuves 2:1, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>726797.1704618235</v>
+        <v>726815</v>
       </c>
       <c r="R2" t="n">
-        <v>6367483.981309837</v>
+        <v>6367494</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,71 +757,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anna Helmersson, Brian Johnson, Sara Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88915684</v>
+        <v>104764390</v>
       </c>
       <c r="B3" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kyrkjuves, Gtl</t>
+          <t>Gammelgarn Kyrkjuves 2:1, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726807.2087415853</v>
+        <v>726800</v>
       </c>
       <c r="R3" t="n">
-        <v>6367468.877637803</v>
+        <v>6367509</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,71 +858,70 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anna Helmersson, Brian Johnson, Sara Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88915708</v>
+        <v>104764391</v>
       </c>
       <c r="B4" t="n">
-        <v>87960</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>970</v>
+        <v>424</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kyrkjuves, Gtl</t>
+          <t>Gammelgarn Kyrkjuves 2:1, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726754.8118339679</v>
+        <v>726752</v>
       </c>
       <c r="R4" t="n">
-        <v>6367662.000959228</v>
+        <v>6367655</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,55 +959,51 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anna Helmersson, Brian Johnson, Sara Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88915705</v>
+        <v>88915651</v>
       </c>
       <c r="B5" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>726806.8505209794</v>
+        <v>726832</v>
       </c>
       <c r="R5" t="n">
-        <v>6367485.059341076</v>
+        <v>6367464</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1046,9 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104764391</v>
+        <v>88915652</v>
       </c>
       <c r="B6" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,40 +1086,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammelgarn Kyrkjuves 2:1, Gtl</t>
+          <t>Kyrkjuves, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>726751.9642158456</v>
+        <v>726859</v>
       </c>
       <c r="R6" t="n">
-        <v>6367654.822346583</v>
+        <v>6367614</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,22 +1140,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,34 +1154,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Brian Johnson, Sara Nilsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104764388</v>
+        <v>88915653</v>
       </c>
       <c r="B7" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,40 +1183,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gammelgarn Kyrkjuves 2:1, Gtl</t>
+          <t>Kyrkjuves, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>726815.0028410841</v>
+        <v>726878</v>
       </c>
       <c r="R7" t="n">
-        <v>6367494.153267145</v>
+        <v>6367635</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,22 +1237,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,75 +1251,66 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Brian Johnson, Sara Nilsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104764357</v>
+        <v>88915708</v>
       </c>
       <c r="B8" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90639</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>970</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelgarn Kyrkjuves 2:1, Gtl</t>
+          <t>Kyrkjuves, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726804.6046771519</v>
+        <v>726755</v>
       </c>
       <c r="R8" t="n">
-        <v>6367505.996523871</v>
+        <v>6367662</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,22 +1334,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,34 +1348,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Brian Johnson, Sara Nilsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104764394</v>
+        <v>104764382</v>
       </c>
       <c r="B9" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,21 +1377,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>2009</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726798.069822543</v>
+        <v>726828</v>
       </c>
       <c r="R9" t="n">
-        <v>6367487.271606363</v>
+        <v>6367501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,19 +1437,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,15 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104764367</v>
+        <v>104764405</v>
       </c>
       <c r="B10" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1603,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726797.5910866009</v>
+        <v>726801</v>
       </c>
       <c r="R10" t="n">
-        <v>6367495.885827219</v>
+        <v>6367485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,19 +1538,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,15 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104764381</v>
+        <v>88915711</v>
       </c>
       <c r="B11" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,40 +1579,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammelgarn Kyrkjuves 2:1, Gtl</t>
+          <t>Kyrkjuves, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726800.7388290267</v>
+        <v>726844</v>
       </c>
       <c r="R11" t="n">
-        <v>6367507.4018227</v>
+        <v>6367499</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,22 +1633,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,56 +1647,50 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Brian Johnson, Sara Nilsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104764365</v>
+        <v>104764306</v>
       </c>
       <c r="B12" t="n">
-        <v>90126</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>232138</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1703,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>726798.9982398552</v>
+        <v>726781</v>
       </c>
       <c r="R12" t="n">
-        <v>6367480.302518194</v>
+        <v>6367506</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,19 +1736,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,56 +1766,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104764400</v>
+        <v>88915705</v>
       </c>
       <c r="B13" t="n">
-        <v>85224</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>248955</v>
+        <v>3712</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelgarn Kyrkjuves 2:1, Gtl</t>
+          <t>Kyrkjuves, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>726798.8794182061</v>
+        <v>726807</v>
       </c>
       <c r="R13" t="n">
-        <v>6367492.17706707</v>
+        <v>6367485</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2008,22 +1831,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,56 +1845,50 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Brian Johnson, Sara Nilsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104764402</v>
+        <v>104764357</v>
       </c>
       <c r="B14" t="n">
-        <v>85318</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,10 +1901,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>726798.759733678</v>
+        <v>726805</v>
       </c>
       <c r="R14" t="n">
-        <v>6367494.330621414</v>
+        <v>6367506</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,19 +1934,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,15 +1964,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104764378</v>
+        <v>104764358</v>
       </c>
       <c r="B15" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,21 +1975,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2210,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>726795.852209087</v>
+        <v>726805</v>
       </c>
       <c r="R15" t="n">
-        <v>6367488.228467271</v>
+        <v>6367491</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,19 +2035,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,37 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104764404</v>
+        <v>104764381</v>
       </c>
       <c r="B16" t="n">
-        <v>85318</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2326,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>726799.570184493</v>
+        <v>726800</v>
       </c>
       <c r="R16" t="n">
-        <v>6367508.957022767</v>
+        <v>6367507</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,19 +2136,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,37 +2166,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104764358</v>
+        <v>104764402</v>
       </c>
       <c r="B17" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2442,10 +2204,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>726804.8731277524</v>
+        <v>726799</v>
       </c>
       <c r="R17" t="n">
-        <v>6367491.430070455</v>
+        <v>6367494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,19 +2237,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,15 +2267,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104764390</v>
+        <v>104764404</v>
       </c>
       <c r="B18" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,21 +2278,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2558,10 +2305,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>726799.570184493</v>
+        <v>726800</v>
       </c>
       <c r="R18" t="n">
-        <v>6367508.957022767</v>
+        <v>6367509</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,19 +2338,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,37 +2368,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104764405</v>
+        <v>104764394</v>
       </c>
       <c r="B19" t="n">
-        <v>89175</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2015</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2674,10 +2406,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>726800.8867229959</v>
+        <v>726798</v>
       </c>
       <c r="R19" t="n">
-        <v>6367485.267947105</v>
+        <v>6367487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2707,19 +2439,9 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,6 +2466,701 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104764365</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gammelgarn Kyrkjuves 2:1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>726799</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6367480</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Brian Johnson, Sara Nilsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>104764400</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gammelgarn Kyrkjuves 2:1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>726799</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6367492</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Brian Johnson, Sara Nilsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>88915693</v>
+      </c>
+      <c r="B22" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kyrkjuves, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>726797</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6367484</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>104764367</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gammelgarn Kyrkjuves 2:1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>726798</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6367496</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Brian Johnson, Sara Nilsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>88915683</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kyrkjuves, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>726832</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6367464</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>88915684</v>
+      </c>
+      <c r="B25" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kyrkjuves, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>726807</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6367469</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>104764378</v>
+      </c>
+      <c r="B26" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gammelgarn Kyrkjuves 2:1, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>726796</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6367488</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Brian Johnson, Sara Nilsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11176-2024 artfynd.xlsx
+++ b/artfynd/A 11176-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764388</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764390</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764391</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88915651</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88915652</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88915653</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88915708</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1464,6 +1504,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764382</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764405</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88915711</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764306</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1860,6 +1920,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88915705</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,6 +2026,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764357</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2062,6 +2132,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764358</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764381</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2264,6 +2344,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764402</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2365,6 +2450,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764404</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2466,6 +2556,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764394</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2567,6 +2662,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764365</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2668,6 +2768,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764400</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2765,6 +2870,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88915693</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2866,6 +2976,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764367</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88915683</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3060,6 +3180,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88915684</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3161,8 +3286,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104764378</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>